--- a/endpoint_excels/iss__securities__security__aggregates.xlsx
+++ b/endpoint_excels/iss__securities__security__aggregates.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="aggregates" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="agregates.dates" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLUMN_DOCS" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +30,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -52,14 +63,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,6 +166,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__securities__s" displayName="TBL_01_iss__securities__s" ref="A1:K13" headerRowCount="1">
+  <autoFilter ref="A1:K13"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="market_name"/>
+    <tableColumn id="4" name="market_title"/>
+    <tableColumn id="5" name="engine"/>
+    <tableColumn id="6" name="tradedate"/>
+    <tableColumn id="7" name="secid"/>
+    <tableColumn id="8" name="value"/>
+    <tableColumn id="9" name="volume"/>
+    <tableColumn id="10" name="numtrades"/>
+    <tableColumn id="11" name="updated_at"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__securities__s" displayName="TBL_02_iss__securities__s" ref="A1:D3" headerRowCount="1">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="ENDPOINT_COLUMN_DOCS" displayName="ENDPOINT_COLUMN_DOCS" ref="A1:C16" headerRowCount="1">
+  <autoFilter ref="A1:C16"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SHEET_NAME"/>
+    <tableColumn id="2" name="COLUMN_NAME"/>
+    <tableColumn id="3" name="DESCRIPTION_RU"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,8 +504,21 @@
   </sheetPr>
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -487,619 +576,622 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>bonds</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Рынок облигаций</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>1735854058</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2887085</v>
-      </c>
-      <c r="J2" t="n">
-        <v>35472</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H2" s="2" t="n">
+        <v>2083481596</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>3466437</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>37428</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ndm</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>repo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Рынок сделок РЕПО</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>37592660937</v>
-      </c>
-      <c r="I4" t="n">
-        <v>84267404</v>
-      </c>
-      <c r="J4" t="n">
-        <v>233</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H4" s="2" t="n">
+        <v>39327962440</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>87450237</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>mamc</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Мультивалютный рынок смешанных активов</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>nonresndm</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок (нерезиденты)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>nonresrepo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Рынок РЕПО (нерезиденты)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:17</t>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>bonds</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Рынок облигаций</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>ndm</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>repo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Рынок сделок РЕПО</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>mamc</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Мультивалютный рынок смешанных активов</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>nonresndm</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок (нерезиденты)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>nonresrepo</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Рынок РЕПО (нерезиденты)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:31</t>
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:16</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1111,74 +1203,377 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>from</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>till</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2021-06-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2021-11-17</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SHEET_NAME</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>COLUMN_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DESCRIPTION_RU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>SECID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>market_name</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>market_title</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>engine</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>tradedate</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>secid</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>numtrades</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>aggregates</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>agregates.dates</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>agregates.dates</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>agregates.dates</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>agregates.dates</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>till</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2021-06-23</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2021-11-17</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-02-13</t>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/endpoint_excels/iss__securities__security__aggregates.xlsx
+++ b/endpoint_excels/iss__securities__security__aggregates.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,16 +29,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -52,14 +62,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -135,6 +162,39 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__securities__s" displayName="TBL_01_iss__securities__s" ref="A1:K13" headerRowCount="1">
+  <autoFilter ref="A1:K13"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="market_name"/>
+    <tableColumn id="4" name="market_title"/>
+    <tableColumn id="5" name="engine"/>
+    <tableColumn id="6" name="tradedate"/>
+    <tableColumn id="7" name="secid"/>
+    <tableColumn id="8" name="value"/>
+    <tableColumn id="9" name="volume"/>
+    <tableColumn id="10" name="numtrades"/>
+    <tableColumn id="11" name="updated_at"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__securities__s" displayName="TBL_02_iss__securities__s" ref="A1:D3" headerRowCount="1">
+  <autoFilter ref="A1:D3"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="from"/>
+    <tableColumn id="4" name="till"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,8 +488,21 @@
   </sheetPr>
   <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -487,612 +560,612 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>bonds</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Рынок облигаций</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>2139560739</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>3560083</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>38831</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>ndm</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="H3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>repo</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Рынок сделок РЕПО</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="2" t="n">
         <v>39327962440</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="2" t="n">
         <v>87450237</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="2" t="n">
         <v>250</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>mamc</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Мультивалютный рынок смешанных активов</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="H5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>nonresndm</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок (нерезиденты)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>nonresrepo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Рынок РЕПО (нерезиденты)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:17</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>bonds</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Рынок облигаций</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>ndm</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>repo</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Рынок сделок РЕПО</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="H10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>mamc</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Мультивалютный рынок смешанных активов</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="H11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>nonresndm</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Режим переговорных сделок (нерезиденты)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="H12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>nonresrepo</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Рынок РЕПО (нерезиденты)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="H13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:16</t>
         </is>
@@ -1100,6 +1173,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1111,8 +1187,14 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -1135,44 +1217,44 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/SU26238RMFS4/aggregates.json</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/securities/RU000A1041Q0/aggregates.json</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2021-11-17</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
@@ -1180,5 +1262,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>